--- a/assets/templates/TUPAD_Import_Blank.xlsx
+++ b/assets/templates/TUPAD_Import_Blank.xlsx
@@ -70,22 +70,22 @@
   </cellStyleXfs>
   <cellXfs count="6">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="1" fillId="2" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment shrinkToFit="0" wrapText="1"/>
+      <alignment shrinkToFit="0" wrapText="1" vertical="center"/>
     </xf>
     <xf borderId="1" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" vertical="center"/>
+      <alignment horizontal="center" readingOrder="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="1" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -322,8 +322,31 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <cols>
+    <col min="1" max="1" width="26" customWidth="1"/>
+    <col min="2" max="2" width="26" customWidth="1"/>
+    <col min="3" max="3" width="26" customWidth="1"/>
+    <col min="4" max="4" width="26" customWidth="1"/>
+    <col min="5" max="5" width="10" customWidth="1"/>
+    <col min="6" max="6" width="20" customWidth="1"/>
+    <col min="7" max="7" width="8" customWidth="1"/>
+    <col min="8" max="8" width="18" customWidth="1"/>
+    <col min="9" max="9" width="22" customWidth="1"/>
+    <col min="10" max="10" width="34" customWidth="1"/>
+    <col min="11" max="11" width="34" customWidth="1"/>
+    <col min="12" max="12" width="18" customWidth="1"/>
+    <col min="13" max="13" width="18" customWidth="1"/>
+    <col min="14" max="14" width="18" customWidth="1"/>
+    <col min="15" max="15" width="22" customWidth="1"/>
+    <col min="16" max="16" width="18" customWidth="1"/>
+    <col min="17" max="17" width="18" customWidth="1"/>
+    <col min="18" max="18" width="18" customWidth="1"/>
+    <col min="19" max="19" width="22" customWidth="1"/>
+    <col min="20" max="20" width="22" customWidth="1"/>
+    <col min="21" max="21" width="22" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="66" customHeight="1">
       <c r="A1" t="inlineStr">
         <is>
           <t>Last Name</t>

--- a/assets/templates/TUPAD_Import_Blank.xlsx
+++ b/assets/templates/TUPAD_Import_Blank.xlsx
@@ -68,7 +68,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="9">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
@@ -86,6 +86,15 @@
     </xf>
     <xf borderId="1" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1" horizontal="center"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1" horizontal="center"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1" horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -347,111 +356,571 @@
   </cols>
   <sheetData>
     <row r="1" ht="66" customHeight="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" t="inlineStr" s="8">
         <is>
           <t>Last Name</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" t="inlineStr" s="8">
         <is>
           <t>First Name</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" t="inlineStr" s="8">
         <is>
           <t>Middle Name</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" t="inlineStr" s="8">
         <is>
           <t>Extension Name</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" t="inlineStr" s="8">
         <is>
           <t>Sex</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" t="inlineStr" s="8">
         <is>
           <t>Date of Birth</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" t="inlineStr" s="8">
         <is>
           <t>Age</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" t="inlineStr" s="8">
         <is>
           <t>Civil Status</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" t="inlineStr" s="8">
         <is>
           <t>Contact Number</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" t="inlineStr" s="8">
         <is>
           <t>Email Address</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" t="inlineStr" s="8">
         <is>
           <t>Complete Address</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" t="inlineStr" s="8">
         <is>
           <t>Barangay</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" t="inlineStr" s="8">
         <is>
           <t>Occupation</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" t="inlineStr" s="8">
         <is>
           <t>Skills</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="O1" t="inlineStr" s="8">
         <is>
           <t>Family Income</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="P1" t="inlineStr" s="8">
         <is>
           <t>Dependents</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="Q1" t="inlineStr" s="8">
         <is>
           <t>ID Type</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="R1" t="inlineStr" s="8">
         <is>
           <t>ID Number</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="S1" t="inlineStr" s="8">
         <is>
           <t>Type of Beneficiary</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="T1" t="inlineStr" s="8">
         <is>
           <t>Dependent Relationship</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="U1" t="inlineStr" s="8">
         <is>
           <t>Interested in Employment</t>
         </is>
       </c>
+    </row>
+    <row r="2" ht="22" customHeight="1">
+      <c r="A2" s="0"/>
+      <c r="B2" s="0"/>
+      <c r="C2" s="0"/>
+      <c r="D2" s="0"/>
+      <c r="E2" s="0"/>
+      <c r="F2" s="0"/>
+      <c r="G2" s="0"/>
+      <c r="H2" s="0"/>
+      <c r="I2" s="0"/>
+      <c r="J2" s="0"/>
+      <c r="K2" s="0"/>
+      <c r="L2" s="0"/>
+      <c r="M2" s="0"/>
+      <c r="N2" s="0"/>
+      <c r="O2" s="0"/>
+      <c r="P2" s="0"/>
+      <c r="Q2" s="0"/>
+      <c r="R2" s="0"/>
+      <c r="S2" s="0"/>
+      <c r="T2" s="0"/>
+      <c r="U2" s="0"/>
+    </row>
+    <row r="3" ht="22" customHeight="1">
+      <c r="A3" s="0"/>
+      <c r="B3" s="0"/>
+      <c r="C3" s="0"/>
+      <c r="D3" s="0"/>
+      <c r="E3" s="0"/>
+      <c r="F3" s="0"/>
+      <c r="G3" s="0"/>
+      <c r="H3" s="0"/>
+      <c r="I3" s="0"/>
+      <c r="J3" s="0"/>
+      <c r="K3" s="0"/>
+      <c r="L3" s="0"/>
+      <c r="M3" s="0"/>
+      <c r="N3" s="0"/>
+      <c r="O3" s="0"/>
+      <c r="P3" s="0"/>
+      <c r="Q3" s="0"/>
+      <c r="R3" s="0"/>
+      <c r="S3" s="0"/>
+      <c r="T3" s="0"/>
+      <c r="U3" s="0"/>
+    </row>
+    <row r="4" ht="22" customHeight="1">
+      <c r="A4" s="0"/>
+      <c r="B4" s="0"/>
+      <c r="C4" s="0"/>
+      <c r="D4" s="0"/>
+      <c r="E4" s="0"/>
+      <c r="F4" s="0"/>
+      <c r="G4" s="0"/>
+      <c r="H4" s="0"/>
+      <c r="I4" s="0"/>
+      <c r="J4" s="0"/>
+      <c r="K4" s="0"/>
+      <c r="L4" s="0"/>
+      <c r="M4" s="0"/>
+      <c r="N4" s="0"/>
+      <c r="O4" s="0"/>
+      <c r="P4" s="0"/>
+      <c r="Q4" s="0"/>
+      <c r="R4" s="0"/>
+      <c r="S4" s="0"/>
+      <c r="T4" s="0"/>
+      <c r="U4" s="0"/>
+    </row>
+    <row r="5" ht="22" customHeight="1">
+      <c r="A5" s="0"/>
+      <c r="B5" s="0"/>
+      <c r="C5" s="0"/>
+      <c r="D5" s="0"/>
+      <c r="E5" s="0"/>
+      <c r="F5" s="0"/>
+      <c r="G5" s="0"/>
+      <c r="H5" s="0"/>
+      <c r="I5" s="0"/>
+      <c r="J5" s="0"/>
+      <c r="K5" s="0"/>
+      <c r="L5" s="0"/>
+      <c r="M5" s="0"/>
+      <c r="N5" s="0"/>
+      <c r="O5" s="0"/>
+      <c r="P5" s="0"/>
+      <c r="Q5" s="0"/>
+      <c r="R5" s="0"/>
+      <c r="S5" s="0"/>
+      <c r="T5" s="0"/>
+      <c r="U5" s="0"/>
+    </row>
+    <row r="6" ht="22" customHeight="1">
+      <c r="A6" s="0"/>
+      <c r="B6" s="0"/>
+      <c r="C6" s="0"/>
+      <c r="D6" s="0"/>
+      <c r="E6" s="0"/>
+      <c r="F6" s="0"/>
+      <c r="G6" s="0"/>
+      <c r="H6" s="0"/>
+      <c r="I6" s="0"/>
+      <c r="J6" s="0"/>
+      <c r="K6" s="0"/>
+      <c r="L6" s="0"/>
+      <c r="M6" s="0"/>
+      <c r="N6" s="0"/>
+      <c r="O6" s="0"/>
+      <c r="P6" s="0"/>
+      <c r="Q6" s="0"/>
+      <c r="R6" s="0"/>
+      <c r="S6" s="0"/>
+      <c r="T6" s="0"/>
+      <c r="U6" s="0"/>
+    </row>
+    <row r="7" ht="22" customHeight="1">
+      <c r="A7" s="0"/>
+      <c r="B7" s="0"/>
+      <c r="C7" s="0"/>
+      <c r="D7" s="0"/>
+      <c r="E7" s="0"/>
+      <c r="F7" s="0"/>
+      <c r="G7" s="0"/>
+      <c r="H7" s="0"/>
+      <c r="I7" s="0"/>
+      <c r="J7" s="0"/>
+      <c r="K7" s="0"/>
+      <c r="L7" s="0"/>
+      <c r="M7" s="0"/>
+      <c r="N7" s="0"/>
+      <c r="O7" s="0"/>
+      <c r="P7" s="0"/>
+      <c r="Q7" s="0"/>
+      <c r="R7" s="0"/>
+      <c r="S7" s="0"/>
+      <c r="T7" s="0"/>
+      <c r="U7" s="0"/>
+    </row>
+    <row r="8" ht="22" customHeight="1">
+      <c r="A8" s="0"/>
+      <c r="B8" s="0"/>
+      <c r="C8" s="0"/>
+      <c r="D8" s="0"/>
+      <c r="E8" s="0"/>
+      <c r="F8" s="0"/>
+      <c r="G8" s="0"/>
+      <c r="H8" s="0"/>
+      <c r="I8" s="0"/>
+      <c r="J8" s="0"/>
+      <c r="K8" s="0"/>
+      <c r="L8" s="0"/>
+      <c r="M8" s="0"/>
+      <c r="N8" s="0"/>
+      <c r="O8" s="0"/>
+      <c r="P8" s="0"/>
+      <c r="Q8" s="0"/>
+      <c r="R8" s="0"/>
+      <c r="S8" s="0"/>
+      <c r="T8" s="0"/>
+      <c r="U8" s="0"/>
+    </row>
+    <row r="9" ht="22" customHeight="1">
+      <c r="A9" s="0"/>
+      <c r="B9" s="0"/>
+      <c r="C9" s="0"/>
+      <c r="D9" s="0"/>
+      <c r="E9" s="0"/>
+      <c r="F9" s="0"/>
+      <c r="G9" s="0"/>
+      <c r="H9" s="0"/>
+      <c r="I9" s="0"/>
+      <c r="J9" s="0"/>
+      <c r="K9" s="0"/>
+      <c r="L9" s="0"/>
+      <c r="M9" s="0"/>
+      <c r="N9" s="0"/>
+      <c r="O9" s="0"/>
+      <c r="P9" s="0"/>
+      <c r="Q9" s="0"/>
+      <c r="R9" s="0"/>
+      <c r="S9" s="0"/>
+      <c r="T9" s="0"/>
+      <c r="U9" s="0"/>
+    </row>
+    <row r="10" ht="22" customHeight="1">
+      <c r="A10" s="0"/>
+      <c r="B10" s="0"/>
+      <c r="C10" s="0"/>
+      <c r="D10" s="0"/>
+      <c r="E10" s="0"/>
+      <c r="F10" s="0"/>
+      <c r="G10" s="0"/>
+      <c r="H10" s="0"/>
+      <c r="I10" s="0"/>
+      <c r="J10" s="0"/>
+      <c r="K10" s="0"/>
+      <c r="L10" s="0"/>
+      <c r="M10" s="0"/>
+      <c r="N10" s="0"/>
+      <c r="O10" s="0"/>
+      <c r="P10" s="0"/>
+      <c r="Q10" s="0"/>
+      <c r="R10" s="0"/>
+      <c r="S10" s="0"/>
+      <c r="T10" s="0"/>
+      <c r="U10" s="0"/>
+    </row>
+    <row r="11" ht="22" customHeight="1">
+      <c r="A11" s="0"/>
+      <c r="B11" s="0"/>
+      <c r="C11" s="0"/>
+      <c r="D11" s="0"/>
+      <c r="E11" s="0"/>
+      <c r="F11" s="0"/>
+      <c r="G11" s="0"/>
+      <c r="H11" s="0"/>
+      <c r="I11" s="0"/>
+      <c r="J11" s="0"/>
+      <c r="K11" s="0"/>
+      <c r="L11" s="0"/>
+      <c r="M11" s="0"/>
+      <c r="N11" s="0"/>
+      <c r="O11" s="0"/>
+      <c r="P11" s="0"/>
+      <c r="Q11" s="0"/>
+      <c r="R11" s="0"/>
+      <c r="S11" s="0"/>
+      <c r="T11" s="0"/>
+      <c r="U11" s="0"/>
+    </row>
+    <row r="12" ht="22" customHeight="1">
+      <c r="A12" s="0"/>
+      <c r="B12" s="0"/>
+      <c r="C12" s="0"/>
+      <c r="D12" s="0"/>
+      <c r="E12" s="0"/>
+      <c r="F12" s="0"/>
+      <c r="G12" s="0"/>
+      <c r="H12" s="0"/>
+      <c r="I12" s="0"/>
+      <c r="J12" s="0"/>
+      <c r="K12" s="0"/>
+      <c r="L12" s="0"/>
+      <c r="M12" s="0"/>
+      <c r="N12" s="0"/>
+      <c r="O12" s="0"/>
+      <c r="P12" s="0"/>
+      <c r="Q12" s="0"/>
+      <c r="R12" s="0"/>
+      <c r="S12" s="0"/>
+      <c r="T12" s="0"/>
+      <c r="U12" s="0"/>
+    </row>
+    <row r="13" ht="22" customHeight="1">
+      <c r="A13" s="0"/>
+      <c r="B13" s="0"/>
+      <c r="C13" s="0"/>
+      <c r="D13" s="0"/>
+      <c r="E13" s="0"/>
+      <c r="F13" s="0"/>
+      <c r="G13" s="0"/>
+      <c r="H13" s="0"/>
+      <c r="I13" s="0"/>
+      <c r="J13" s="0"/>
+      <c r="K13" s="0"/>
+      <c r="L13" s="0"/>
+      <c r="M13" s="0"/>
+      <c r="N13" s="0"/>
+      <c r="O13" s="0"/>
+      <c r="P13" s="0"/>
+      <c r="Q13" s="0"/>
+      <c r="R13" s="0"/>
+      <c r="S13" s="0"/>
+      <c r="T13" s="0"/>
+      <c r="U13" s="0"/>
+    </row>
+    <row r="14" ht="22" customHeight="1">
+      <c r="A14" s="0"/>
+      <c r="B14" s="0"/>
+      <c r="C14" s="0"/>
+      <c r="D14" s="0"/>
+      <c r="E14" s="0"/>
+      <c r="F14" s="0"/>
+      <c r="G14" s="0"/>
+      <c r="H14" s="0"/>
+      <c r="I14" s="0"/>
+      <c r="J14" s="0"/>
+      <c r="K14" s="0"/>
+      <c r="L14" s="0"/>
+      <c r="M14" s="0"/>
+      <c r="N14" s="0"/>
+      <c r="O14" s="0"/>
+      <c r="P14" s="0"/>
+      <c r="Q14" s="0"/>
+      <c r="R14" s="0"/>
+      <c r="S14" s="0"/>
+      <c r="T14" s="0"/>
+      <c r="U14" s="0"/>
+    </row>
+    <row r="15" ht="22" customHeight="1">
+      <c r="A15" s="0"/>
+      <c r="B15" s="0"/>
+      <c r="C15" s="0"/>
+      <c r="D15" s="0"/>
+      <c r="E15" s="0"/>
+      <c r="F15" s="0"/>
+      <c r="G15" s="0"/>
+      <c r="H15" s="0"/>
+      <c r="I15" s="0"/>
+      <c r="J15" s="0"/>
+      <c r="K15" s="0"/>
+      <c r="L15" s="0"/>
+      <c r="M15" s="0"/>
+      <c r="N15" s="0"/>
+      <c r="O15" s="0"/>
+      <c r="P15" s="0"/>
+      <c r="Q15" s="0"/>
+      <c r="R15" s="0"/>
+      <c r="S15" s="0"/>
+      <c r="T15" s="0"/>
+      <c r="U15" s="0"/>
+    </row>
+    <row r="16" ht="22" customHeight="1">
+      <c r="A16" s="0"/>
+      <c r="B16" s="0"/>
+      <c r="C16" s="0"/>
+      <c r="D16" s="0"/>
+      <c r="E16" s="0"/>
+      <c r="F16" s="0"/>
+      <c r="G16" s="0"/>
+      <c r="H16" s="0"/>
+      <c r="I16" s="0"/>
+      <c r="J16" s="0"/>
+      <c r="K16" s="0"/>
+      <c r="L16" s="0"/>
+      <c r="M16" s="0"/>
+      <c r="N16" s="0"/>
+      <c r="O16" s="0"/>
+      <c r="P16" s="0"/>
+      <c r="Q16" s="0"/>
+      <c r="R16" s="0"/>
+      <c r="S16" s="0"/>
+      <c r="T16" s="0"/>
+      <c r="U16" s="0"/>
+    </row>
+    <row r="17" ht="22" customHeight="1">
+      <c r="A17" s="0"/>
+      <c r="B17" s="0"/>
+      <c r="C17" s="0"/>
+      <c r="D17" s="0"/>
+      <c r="E17" s="0"/>
+      <c r="F17" s="0"/>
+      <c r="G17" s="0"/>
+      <c r="H17" s="0"/>
+      <c r="I17" s="0"/>
+      <c r="J17" s="0"/>
+      <c r="K17" s="0"/>
+      <c r="L17" s="0"/>
+      <c r="M17" s="0"/>
+      <c r="N17" s="0"/>
+      <c r="O17" s="0"/>
+      <c r="P17" s="0"/>
+      <c r="Q17" s="0"/>
+      <c r="R17" s="0"/>
+      <c r="S17" s="0"/>
+      <c r="T17" s="0"/>
+      <c r="U17" s="0"/>
+    </row>
+    <row r="18" ht="22" customHeight="1">
+      <c r="A18" s="0"/>
+      <c r="B18" s="0"/>
+      <c r="C18" s="0"/>
+      <c r="D18" s="0"/>
+      <c r="E18" s="0"/>
+      <c r="F18" s="0"/>
+      <c r="G18" s="0"/>
+      <c r="H18" s="0"/>
+      <c r="I18" s="0"/>
+      <c r="J18" s="0"/>
+      <c r="K18" s="0"/>
+      <c r="L18" s="0"/>
+      <c r="M18" s="0"/>
+      <c r="N18" s="0"/>
+      <c r="O18" s="0"/>
+      <c r="P18" s="0"/>
+      <c r="Q18" s="0"/>
+      <c r="R18" s="0"/>
+      <c r="S18" s="0"/>
+      <c r="T18" s="0"/>
+      <c r="U18" s="0"/>
+    </row>
+    <row r="19" ht="22" customHeight="1">
+      <c r="A19" s="0"/>
+      <c r="B19" s="0"/>
+      <c r="C19" s="0"/>
+      <c r="D19" s="0"/>
+      <c r="E19" s="0"/>
+      <c r="F19" s="0"/>
+      <c r="G19" s="0"/>
+      <c r="H19" s="0"/>
+      <c r="I19" s="0"/>
+      <c r="J19" s="0"/>
+      <c r="K19" s="0"/>
+      <c r="L19" s="0"/>
+      <c r="M19" s="0"/>
+      <c r="N19" s="0"/>
+      <c r="O19" s="0"/>
+      <c r="P19" s="0"/>
+      <c r="Q19" s="0"/>
+      <c r="R19" s="0"/>
+      <c r="S19" s="0"/>
+      <c r="T19" s="0"/>
+      <c r="U19" s="0"/>
+    </row>
+    <row r="20" ht="22" customHeight="1">
+      <c r="A20" s="0"/>
+      <c r="B20" s="0"/>
+      <c r="C20" s="0"/>
+      <c r="D20" s="0"/>
+      <c r="E20" s="0"/>
+      <c r="F20" s="0"/>
+      <c r="G20" s="0"/>
+      <c r="H20" s="0"/>
+      <c r="I20" s="0"/>
+      <c r="J20" s="0"/>
+      <c r="K20" s="0"/>
+      <c r="L20" s="0"/>
+      <c r="M20" s="0"/>
+      <c r="N20" s="0"/>
+      <c r="O20" s="0"/>
+      <c r="P20" s="0"/>
+      <c r="Q20" s="0"/>
+      <c r="R20" s="0"/>
+      <c r="S20" s="0"/>
+      <c r="T20" s="0"/>
+      <c r="U20" s="0"/>
+    </row>
+    <row r="21" ht="22" customHeight="1">
+      <c r="A21" s="0"/>
+      <c r="B21" s="0"/>
+      <c r="C21" s="0"/>
+      <c r="D21" s="0"/>
+      <c r="E21" s="0"/>
+      <c r="F21" s="0"/>
+      <c r="G21" s="0"/>
+      <c r="H21" s="0"/>
+      <c r="I21" s="0"/>
+      <c r="J21" s="0"/>
+      <c r="K21" s="0"/>
+      <c r="L21" s="0"/>
+      <c r="M21" s="0"/>
+      <c r="N21" s="0"/>
+      <c r="O21" s="0"/>
+      <c r="P21" s="0"/>
+      <c r="Q21" s="0"/>
+      <c r="R21" s="0"/>
+      <c r="S21" s="0"/>
+      <c r="T21" s="0"/>
+      <c r="U21" s="0"/>
     </row>
   </sheetData>
 </worksheet>

--- a/assets/templates/TUPAD_Import_Blank.xlsx
+++ b/assets/templates/TUPAD_Import_Blank.xlsx
@@ -433,7 +433,7 @@
       </c>
       <c r="P1" t="inlineStr" s="8">
         <is>
-          <t>Dependents</t>
+          <t>Dependent Name</t>
         </is>
       </c>
       <c r="Q1" t="inlineStr" s="8">
